--- a/restaurant_crawler/restaurant_data_台北_麻辣鍋_20250910_135238_with_emails.xlsx
+++ b/restaurant_crawler/restaurant_data_台北_麻辣鍋_20250910_135238_with_emails.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\slow3\OneDrive\桌面\GitHubProjects\BYOB\restaurant_crawler\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F31F43B2-5015-4B12-AC8D-065986A04F0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52B94D3F-9F7A-46E9-8D32-F007F220A8CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="257">
   <si>
     <t>name</t>
   </si>
@@ -376,21 +376,6 @@
     <t>fatdohp@gmail.com</t>
   </si>
   <si>
-    <t>九寨十鍋-中山旗艦店</t>
-  </si>
-  <si>
-    <t>10491台灣台北市中山區中山北路二段6號</t>
-  </si>
-  <si>
-    <t>02 2511 1172</t>
-  </si>
-  <si>
-    <t>https://reserve.oddle.me/jiuzhaishiguo</t>
-  </si>
-  <si>
-    <t>ChIJn8ziUgCpQjQREpNVnSujP7E</t>
-  </si>
-  <si>
     <t>向辣 麻辣鍋吃到飽 台北西門店</t>
   </si>
   <si>
@@ -641,18 +626,6 @@
   </si>
   <si>
     <t>ChIJW8UfsbCrQjQRoRrXeqzVk5g</t>
-  </si>
-  <si>
-    <t>青花驕麻辣鍋 新店民權店</t>
-  </si>
-  <si>
-    <t>23141台灣新北市新店區民權路100號1F</t>
-  </si>
-  <si>
-    <t>02 2218 0931</t>
-  </si>
-  <si>
-    <t>ChIJZwjK46wDaDQReLWXYaGvuZY</t>
   </si>
   <si>
     <t>辛殿麻辣鍋｜松江店</t>
@@ -1381,28 +1354,28 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="B7" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="C7" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="E7">
         <v>4.9000000000000004</v>
       </c>
       <c r="F7">
-        <v>6361</v>
+        <v>18966</v>
       </c>
       <c r="G7" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="H7" t="s">
-        <v>111</v>
+        <v>128</v>
       </c>
       <c r="I7" t="s">
         <v>26</v>
@@ -1410,28 +1383,28 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="B8" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="C8" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="E8">
-        <v>4.9000000000000004</v>
+        <v>4.2</v>
       </c>
       <c r="F8">
-        <v>18966</v>
+        <v>6847</v>
       </c>
       <c r="G8" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="H8" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="I8" t="s">
         <v>26</v>
@@ -1439,28 +1412,28 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B9" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C9" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E9">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="F9">
-        <v>6847</v>
+        <v>1409</v>
       </c>
       <c r="G9" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I9" t="s">
         <v>26</v>
@@ -1468,28 +1441,28 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>145</v>
+        <v>166</v>
       </c>
       <c r="B10" t="s">
-        <v>146</v>
+        <v>167</v>
       </c>
       <c r="C10" t="s">
-        <v>147</v>
+        <v>168</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>148</v>
+        <v>169</v>
       </c>
       <c r="E10">
-        <v>4.5</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="F10">
-        <v>1409</v>
+        <v>1204</v>
       </c>
       <c r="G10" t="s">
-        <v>149</v>
+        <v>170</v>
       </c>
       <c r="H10" t="s">
-        <v>150</v>
+        <v>171</v>
       </c>
       <c r="I10" t="s">
         <v>26</v>
@@ -1497,28 +1470,28 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
       <c r="B11" t="s">
-        <v>172</v>
+        <v>187</v>
       </c>
       <c r="C11" t="s">
-        <v>173</v>
+        <v>188</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="E11">
-        <v>4.9000000000000004</v>
+        <v>4.2</v>
       </c>
       <c r="F11">
-        <v>1204</v>
+        <v>2525</v>
       </c>
       <c r="G11" t="s">
-        <v>175</v>
+        <v>190</v>
       </c>
       <c r="H11" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="I11" t="s">
         <v>26</v>
@@ -1526,28 +1499,28 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>191</v>
+        <v>206</v>
       </c>
       <c r="B12" t="s">
-        <v>192</v>
+        <v>207</v>
       </c>
       <c r="C12" t="s">
-        <v>193</v>
+        <v>208</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>194</v>
+        <v>209</v>
       </c>
       <c r="E12">
-        <v>4.2</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="F12">
-        <v>2525</v>
+        <v>5499</v>
       </c>
       <c r="G12" t="s">
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="H12" t="s">
-        <v>196</v>
+        <v>211</v>
       </c>
       <c r="I12" t="s">
         <v>26</v>
@@ -1555,88 +1528,30 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>207</v>
+        <v>246</v>
       </c>
       <c r="B13" t="s">
-        <v>208</v>
+        <v>247</v>
       </c>
       <c r="C13" t="s">
-        <v>209</v>
+        <v>248</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>82</v>
+        <v>249</v>
       </c>
       <c r="E13">
         <v>4.9000000000000004</v>
       </c>
       <c r="F13">
-        <v>15822</v>
+        <v>741</v>
       </c>
       <c r="G13" t="s">
-        <v>210</v>
+        <v>250</v>
       </c>
       <c r="H13" t="s">
-        <v>84</v>
+        <v>251</v>
       </c>
       <c r="I13" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>215</v>
-      </c>
-      <c r="B14" t="s">
-        <v>216</v>
-      </c>
-      <c r="C14" t="s">
-        <v>217</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="E14">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="F14">
-        <v>5499</v>
-      </c>
-      <c r="G14" t="s">
-        <v>219</v>
-      </c>
-      <c r="H14" t="s">
-        <v>220</v>
-      </c>
-      <c r="I14" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>255</v>
-      </c>
-      <c r="B15" t="s">
-        <v>256</v>
-      </c>
-      <c r="C15" t="s">
-        <v>257</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="E15">
-        <v>4.9000000000000004</v>
-      </c>
-      <c r="F15">
-        <v>741</v>
-      </c>
-      <c r="G15" t="s">
-        <v>259</v>
-      </c>
-      <c r="H15" t="s">
-        <v>260</v>
-      </c>
-      <c r="I15" t="s">
         <v>26</v>
       </c>
     </row>
@@ -2049,16 +1964,16 @@
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="B32" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="C32" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="D32" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="E32">
         <v>4.9000000000000004</v>
@@ -2067,7 +1982,7 @@
         <v>11809</v>
       </c>
       <c r="G32" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="I32" t="s">
         <v>14</v>
@@ -2075,16 +1990,16 @@
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="B33" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="C33" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="D33" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="E33">
         <v>4.8</v>
@@ -2093,7 +2008,7 @@
         <v>1063</v>
       </c>
       <c r="G33" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="I33" t="s">
         <v>14</v>
@@ -2101,16 +2016,16 @@
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="B34" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="C34" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="D34" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="E34">
         <v>4.9000000000000004</v>
@@ -2119,7 +2034,7 @@
         <v>672</v>
       </c>
       <c r="G34" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="I34" t="s">
         <v>14</v>
@@ -2127,16 +2042,16 @@
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="B35" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="C35" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="D35" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="E35">
         <v>4.7</v>
@@ -2145,7 +2060,7 @@
         <v>3194</v>
       </c>
       <c r="G35" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="I35" t="s">
         <v>14</v>
@@ -2153,16 +2068,16 @@
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="B36" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="C36" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="D36" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="E36">
         <v>4.7</v>
@@ -2171,7 +2086,7 @@
         <v>8648</v>
       </c>
       <c r="G36" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="I36" t="s">
         <v>14</v>
@@ -2179,16 +2094,16 @@
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="B37" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="C37" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="D37" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="E37">
         <v>4.3</v>
@@ -2197,7 +2112,7 @@
         <v>4734</v>
       </c>
       <c r="G37" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="I37" t="s">
         <v>14</v>
@@ -2205,13 +2120,13 @@
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="B38" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="C38" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="E38">
         <v>4.4000000000000004</v>
@@ -2220,7 +2135,7 @@
         <v>5188</v>
       </c>
       <c r="G38" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="I38" t="s">
         <v>14</v>
@@ -2228,16 +2143,16 @@
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="B39" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="C39" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="D39" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="E39">
         <v>4.5999999999999996</v>
@@ -2246,7 +2161,7 @@
         <v>5648</v>
       </c>
       <c r="G39" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="I39" t="s">
         <v>14</v>
@@ -2254,16 +2169,16 @@
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="B40" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="C40" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="D40" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="E40">
         <v>4.9000000000000004</v>
@@ -2272,7 +2187,7 @@
         <v>13009</v>
       </c>
       <c r="G40" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="I40" t="s">
         <v>14</v>
@@ -2280,16 +2195,16 @@
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="B41" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="C41" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="D41" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="E41">
         <v>4.7</v>
@@ -2298,7 +2213,7 @@
         <v>4733</v>
       </c>
       <c r="G41" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="I41" t="s">
         <v>14</v>
@@ -2306,16 +2221,16 @@
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="B42" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="C42" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="D42" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="E42">
         <v>4.2</v>
@@ -2324,7 +2239,7 @@
         <v>5465</v>
       </c>
       <c r="G42" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="I42" t="s">
         <v>14</v>
@@ -2332,16 +2247,16 @@
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="B43" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="C43" t="s">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="D43" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="E43">
         <v>4.4000000000000004</v>
@@ -2350,7 +2265,7 @@
         <v>7031</v>
       </c>
       <c r="G43" t="s">
-        <v>214</v>
+        <v>205</v>
       </c>
       <c r="I43" t="s">
         <v>14</v>
@@ -2358,16 +2273,16 @@
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="B44" t="s">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="C44" t="s">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="D44" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="E44">
         <v>4.4000000000000004</v>
@@ -2376,7 +2291,7 @@
         <v>11827</v>
       </c>
       <c r="G44" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="I44" t="s">
         <v>14</v>
@@ -2384,13 +2299,13 @@
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="B45" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="D45" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="E45">
         <v>4.9000000000000004</v>
@@ -2399,7 +2314,7 @@
         <v>7</v>
       </c>
       <c r="G45" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="I45" t="s">
         <v>14</v>
@@ -2407,16 +2322,16 @@
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="B46" t="s">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="C46" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="D46" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="E46">
         <v>4.5999999999999996</v>
@@ -2425,7 +2340,7 @@
         <v>1603</v>
       </c>
       <c r="G46" t="s">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="I46" t="s">
         <v>14</v>
@@ -2433,16 +2348,16 @@
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="B47" t="s">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="C47" t="s">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="D47" t="s">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="E47">
         <v>4.5999999999999996</v>
@@ -2451,7 +2366,7 @@
         <v>1591</v>
       </c>
       <c r="G47" t="s">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="I47" t="s">
         <v>14</v>
@@ -2459,16 +2374,16 @@
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="B48" t="s">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="C48" t="s">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="D48" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="E48">
         <v>4.9000000000000004</v>
@@ -2477,7 +2392,7 @@
         <v>2456</v>
       </c>
       <c r="G48" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="I48" t="s">
         <v>14</v>
@@ -2485,16 +2400,16 @@
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="B49" t="s">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="C49" t="s">
-        <v>247</v>
+        <v>238</v>
       </c>
       <c r="D49" t="s">
-        <v>248</v>
+        <v>239</v>
       </c>
       <c r="E49">
         <v>4.9000000000000004</v>
@@ -2503,7 +2418,7 @@
         <v>2875</v>
       </c>
       <c r="G49" t="s">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="I49" t="s">
         <v>14</v>
@@ -2511,16 +2426,16 @@
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="B50" t="s">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="C50" t="s">
-        <v>252</v>
+        <v>243</v>
       </c>
       <c r="D50" t="s">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="E50">
         <v>4.7</v>
@@ -2529,7 +2444,7 @@
         <v>5253</v>
       </c>
       <c r="G50" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="I50" t="s">
         <v>14</v>
@@ -2537,16 +2452,16 @@
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>261</v>
+        <v>252</v>
       </c>
       <c r="B51" t="s">
-        <v>262</v>
+        <v>253</v>
       </c>
       <c r="C51" t="s">
-        <v>263</v>
+        <v>254</v>
       </c>
       <c r="D51" t="s">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="E51">
         <v>4.3</v>
@@ -2555,7 +2470,7 @@
         <v>934</v>
       </c>
       <c r="G51" t="s">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="I51" t="s">
         <v>14</v>

--- a/restaurant_crawler/restaurant_data_台北_麻辣鍋_20250910_135238_with_emails.xlsx
+++ b/restaurant_crawler/restaurant_data_台北_麻辣鍋_20250910_135238_with_emails.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\slow3\OneDrive\桌面\GitHubProjects\BYOB\restaurant_crawler\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52B94D3F-9F7A-46E9-8D32-F007F220A8CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B631ABB9-CA75-48CD-944C-0E9BDD21FA71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="167">
   <si>
     <t>name</t>
   </si>
@@ -67,21 +67,6 @@
     <t>not_found</t>
   </si>
   <si>
-    <t>詹記麻辣火鍋-西門大世界</t>
-  </si>
-  <si>
-    <t>10844台灣台北市萬華區成都路81號B1</t>
-  </si>
-  <si>
-    <t>02 2311 1800</t>
-  </si>
-  <si>
-    <t>https://inline.app/booking/-KO9-zyZTRpTH7LNAe99/-NvFDHdbyHM7P2vbgoDP?language=zh-tw</t>
-  </si>
-  <si>
-    <t>ChIJSWfsRKOpQjQRVKGICjE3XPU</t>
-  </si>
-  <si>
     <t>皇家帝國麻辣火鍋</t>
   </si>
   <si>
@@ -127,66 +112,9 @@
     <t>02 2722 0557</t>
   </si>
   <si>
-    <t>https://shougongdian.com.tw/</t>
-  </si>
-  <si>
     <t>ChIJzdC1klSrQjQRCM9hRORZX18</t>
   </si>
   <si>
-    <t>問鼎 ‧ 皇上吉祥 麻辣養生鍋-忠孝店</t>
-  </si>
-  <si>
-    <t>106台灣台北市大安區忠孝東路四段210號2樓</t>
-  </si>
-  <si>
-    <t>02 2731 2107</t>
-  </si>
-  <si>
-    <t>ChIJWedVvsWrQjQRbOOIa7ofL2s</t>
-  </si>
-  <si>
-    <t>青花驕麻辣鍋 台北中山北店</t>
-  </si>
-  <si>
-    <t>10491台灣台北市中山區中山北路一段137號</t>
-  </si>
-  <si>
-    <t>02 2511 1097</t>
-  </si>
-  <si>
-    <t>https://www.chinhuajiao.com/</t>
-  </si>
-  <si>
-    <t>ChIJvS1updypQjQRDINLLoAUlDY</t>
-  </si>
-  <si>
-    <t>紅九九個人麻辣鴛鴦鍋</t>
-  </si>
-  <si>
-    <t>105台灣台北市松山區南京東路四段179巷3號</t>
-  </si>
-  <si>
-    <t>02 8786 7299</t>
-  </si>
-  <si>
-    <t>https://www.hongjojo99.com.tw/</t>
-  </si>
-  <si>
-    <t>ChIJm0t2xferQjQRmVfNQBTAGm4</t>
-  </si>
-  <si>
-    <t>滿大人頂級麻辣鴛鴦鍋-吃到飽</t>
-  </si>
-  <si>
-    <t>10491台灣台北市中山區民權東路二段7號</t>
-  </si>
-  <si>
-    <t>02 2597 0011</t>
-  </si>
-  <si>
-    <t>ChIJc6ZuBQCpQjQRX70DFx9HUjQ</t>
-  </si>
-  <si>
     <t>問鼎 ‧ 皇上吉祥 麻辣養生鍋-西門店</t>
   </si>
   <si>
@@ -217,33 +145,6 @@
     <t>ChIJe1bzLwCrQjQRhdP7Iph-X08</t>
   </si>
   <si>
-    <t>初殿鍋物-永春店「最後收客2100」平日套餐299元享60種自助吧｜寵物友善｜被火鍋耽誤的滷肉飯｜牛奶鍋｜麻辣鍋｜台北火鍋、美食、餐廳、restaurant</t>
-  </si>
-  <si>
-    <t>110台灣台北市信義區虎林街132巷21號</t>
-  </si>
-  <si>
-    <t>02 2722 0613</t>
-  </si>
-  <si>
-    <t>https://lin.ee/YsKjgDj</t>
-  </si>
-  <si>
-    <t>ChIJCXSBy6CrQjQRw8vYP_S9lwQ</t>
-  </si>
-  <si>
-    <t>老四川巴蜀麻辣燙 台北南京店</t>
-  </si>
-  <si>
-    <t>104台灣台北市中山區南京東路二段45號</t>
-  </si>
-  <si>
-    <t>02 2522 3333</t>
-  </si>
-  <si>
-    <t>ChIJb4jl7mapQjQRZLMs-DXlKeI</t>
-  </si>
-  <si>
     <t>無老鍋(台北信義店)</t>
   </si>
   <si>
@@ -310,36 +211,6 @@
     <t>ChIJUUp8Vm-pQjQRQIVDxFaJEgo</t>
   </si>
   <si>
-    <t>麻神麻辣火鍋</t>
-  </si>
-  <si>
-    <t>105台灣台北市松山區南京東路五段8號3樓</t>
-  </si>
-  <si>
-    <t>02 2749 2508</t>
-  </si>
-  <si>
-    <t>https://www.mashenpot.com.tw/</t>
-  </si>
-  <si>
-    <t>ChIJSccI3uqrQjQREb1Jq5ru4GU</t>
-  </si>
-  <si>
-    <t>說故事黃金雞湯鍋（台北大安區必吃火鍋推薦／台北東區忠孝東路聚餐餐廳／半夜好吃凌晨宵夜美食）</t>
-  </si>
-  <si>
-    <t>106台灣台北市大安區忠孝東路四段181巷40弄13號</t>
-  </si>
-  <si>
-    <t>02 2771 9100</t>
-  </si>
-  <si>
-    <t>https://reurl.cc/O5m87X</t>
-  </si>
-  <si>
-    <t>ChIJgTdWJZWrQjQRD85HeKVlE2w</t>
-  </si>
-  <si>
     <t>四川龍府</t>
   </si>
   <si>
@@ -475,21 +346,6 @@
     <t>ChIJyR1obwCrQjQR2mwjm6lKXjs</t>
   </si>
   <si>
-    <t>豪饌頂級麻辣火鍋吃到飽(錦州店)-中山美食•海鮮•肉品•日本A5和牛/日本干貝/龍蝦吃到飽</t>
-  </si>
-  <si>
-    <t>104台灣台北市中山區錦州街32號2樓</t>
-  </si>
-  <si>
-    <t>02 2511 0669</t>
-  </si>
-  <si>
-    <t>https://inline.app/booking/haorichhotpot</t>
-  </si>
-  <si>
-    <t>ChIJmQvrH4upQjQRVv23J0WuYFs</t>
-  </si>
-  <si>
     <t>這一鍋 台北信義殿</t>
   </si>
   <si>
@@ -499,27 +355,9 @@
     <t>02 2708 1111</t>
   </si>
   <si>
-    <t>http://www.toponepot.com/</t>
-  </si>
-  <si>
     <t>ChIJXzHnYtKrQjQR2CAASg5xRLw</t>
   </si>
   <si>
-    <t>辛殿麻辣鍋｜公館店</t>
-  </si>
-  <si>
-    <t>100台灣台北市中正區羅斯福路三段316巷9弄1號</t>
-  </si>
-  <si>
-    <t>02 7733 7667</t>
-  </si>
-  <si>
-    <t>https://inline.app/order/-LDKPhTT6bNhwjRVHpC2/-MWbDrcVGUuDMkYvCrz7?language=zh-tw</t>
-  </si>
-  <si>
-    <t>ChIJfS17_zypQjQRJX74ClxumPI</t>
-  </si>
-  <si>
     <t>岩漿漢方麻辣火鍋-微風信義店</t>
   </si>
   <si>
@@ -538,18 +376,6 @@
     <t>m02yenchiang@gmail.com</t>
   </si>
   <si>
-    <t>太和殿鴛鴦麻辣火鍋</t>
-  </si>
-  <si>
-    <t>106台灣台北市大安區信義路四段315號</t>
-  </si>
-  <si>
-    <t>02 2705 0909</t>
-  </si>
-  <si>
-    <t>ChIJ_z7E28urQjQRAWHwki-BPDE</t>
-  </si>
-  <si>
     <t>新馬辣經典麻辣鍋 昆明店</t>
   </si>
   <si>
@@ -565,21 +391,6 @@
     <t>ChIJG4wq2QipQjQRRHxq9Slwd80</t>
   </si>
   <si>
-    <t>汆牛 溫體牛肉火鍋-西門店</t>
-  </si>
-  <si>
-    <t>108台灣台北市萬華區成都路141號</t>
-  </si>
-  <si>
-    <t>02 2388 9299</t>
-  </si>
-  <si>
-    <t>https://inline.app/booking/-NhkfZc1EIRc-6y8Si0q:inline-live-3/-OWIcKosRxS-k0PQ_9Sc</t>
-  </si>
-  <si>
-    <t>ChIJY2ONLcupQjQRYr_cRA1MpU4</t>
-  </si>
-  <si>
     <t>椒心苑麻辣鍋</t>
   </si>
   <si>
@@ -598,48 +409,6 @@
     <t>chiaohsinyuan22@gmail.com</t>
   </si>
   <si>
-    <t>食一鍋火鍋-高CP台北火鍋-永和人氣鍋物|平價火鍋|必吃火鍋|在地推薦火鍋|必吃涮涮鍋|特色火鍋|寵物友善火鍋|熱門火鍋</t>
-  </si>
-  <si>
-    <t>234台灣新北市永和區林森路91號</t>
-  </si>
-  <si>
-    <t>02 2926 6169</t>
-  </si>
-  <si>
-    <t>http://www.eatonehotpot.com/</t>
-  </si>
-  <si>
-    <t>ChIJYR7Hiv-pQjQRswkpB96F7K0</t>
-  </si>
-  <si>
-    <t>辛殿麻辣鍋｜信義店</t>
-  </si>
-  <si>
-    <t>110台灣台北市信義區松壽路28號</t>
-  </si>
-  <si>
-    <t>02 2722 7667</t>
-  </si>
-  <si>
-    <t>https://inline.app/booking/-LDKPhTT6bNhwjRVHpC2?language=zh-tw&amp;fbclid=IwAR39ynHxUYIhofgXcYEJIKo5fn5Mza9gf8eBEV1pZ_IbAIMdn3bb3yAbigc</t>
-  </si>
-  <si>
-    <t>ChIJW8UfsbCrQjQRoRrXeqzVk5g</t>
-  </si>
-  <si>
-    <t>辛殿麻辣鍋｜松江店</t>
-  </si>
-  <si>
-    <t>10491台灣台北市中山區松江路129-4號</t>
-  </si>
-  <si>
-    <t>02 2503 7667</t>
-  </si>
-  <si>
-    <t>ChIJK5H6kWCpQjQR6TAsgX00Cys</t>
-  </si>
-  <si>
     <t>老四川巴蜀麻辣燙 台北長安店</t>
   </si>
   <si>
@@ -658,21 +427,6 @@
     <t>ec@oldsichuan.com.tw</t>
   </si>
   <si>
-    <t>馬辣頂級麻辣鴛鴦火鍋 西門店</t>
-  </si>
-  <si>
-    <t>108台灣台北市萬華區西寧南路157號2f</t>
-  </si>
-  <si>
-    <t>02 2314 6528</t>
-  </si>
-  <si>
-    <t>https://www.mala.com.tw/Home/BrandIndex?verificationCode=5F3863B104D33FAF3A27B2A7F4E7183D</t>
-  </si>
-  <si>
-    <t>ChIJGaoLGQmpQjQRZee3w4A0D-A</t>
-  </si>
-  <si>
     <t>麻辣鍋 台北西門町店</t>
   </si>
   <si>
@@ -715,51 +469,6 @@
     <t>ChIJj1sXfN6rQjQRQQzAZzfGjN8</t>
   </si>
   <si>
-    <t>旬味 自然鍋物-台北美食 信義區美食 信義區火鍋 信義區火鍋推薦 信義區好吃推薦 信義區高CP值火鍋鍋物 火鍋推薦 寵物友善</t>
-  </si>
-  <si>
-    <t>110台灣台北市信義區逸仙路50巷18號</t>
-  </si>
-  <si>
-    <t>02 2720 0873</t>
-  </si>
-  <si>
-    <t>https://inline.app/booking/-NGpHd7RFLo4ttBwoWYX:inline-live-3/-NGpHdKFIkkvtH9_-g_n?language=zh-tw</t>
-  </si>
-  <si>
-    <t>ChIJZVGPdlCrQjQRYQbyyBX7IaI</t>
-  </si>
-  <si>
-    <t>沐澄鴛鴦鍋</t>
-  </si>
-  <si>
-    <t>105台灣台北市松山區光復北路98號2樓</t>
-  </si>
-  <si>
-    <t>02 2578 9696</t>
-  </si>
-  <si>
-    <t>https://www.instagram.com/muchang__hotpot?igsh=ZWw4djMycTloMDVu</t>
-  </si>
-  <si>
-    <t>ChIJ6dds7zarQjQRRbOIzfP9_WI</t>
-  </si>
-  <si>
-    <t>新馬辣經典麻辣鍋-信義遠百店Plus+</t>
-  </si>
-  <si>
-    <t>110台灣台北市信義區松仁路58號遠東百貨 信義A1314樓</t>
-  </si>
-  <si>
-    <t>02 2720 2118</t>
-  </si>
-  <si>
-    <t>https://www.mala.com.tw/</t>
-  </si>
-  <si>
-    <t>ChIJ37CXh_OrQjQR6y3sejsXmhk</t>
-  </si>
-  <si>
     <t>三分半海鮮鍋物</t>
   </si>
   <si>
@@ -791,6 +500,27 @@
   </si>
   <si>
     <t>ChIJSeEGna-rQjQR67y_sDHUntA</t>
+  </si>
+  <si>
+    <t>shouwuzdaogrouphospitality@gmail.com</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/shougongdian/?locale=zh_TW&amp;utm_source=utm_OW</t>
+  </si>
+  <si>
+    <t>service01@tripodking.com.tw</t>
+  </si>
+  <si>
+    <t>marketing@xiangla.com.tw</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/toponepot/</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> market@jhujian.com.tw</t>
+  </si>
+  <si>
+    <t>service@tripodking.com.tw</t>
   </si>
 </sst>
 </file>
@@ -1169,7 +899,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I51"/>
+  <dimension ref="A1:K31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -1209,16 +939,16 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E2">
         <v>4.9000000000000004</v>
@@ -1227,27 +957,27 @@
         <v>100557</v>
       </c>
       <c r="G2" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="H2" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="I2" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>79</v>
+        <v>46</v>
       </c>
       <c r="B3" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="C3" t="s">
-        <v>81</v>
+        <v>48</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>82</v>
+        <v>49</v>
       </c>
       <c r="E3">
         <v>4.9000000000000004</v>
@@ -1256,27 +986,27 @@
         <v>14267</v>
       </c>
       <c r="G3" t="s">
-        <v>83</v>
+        <v>50</v>
       </c>
       <c r="H3" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="I3" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>85</v>
+        <v>52</v>
       </c>
       <c r="B4" t="s">
-        <v>86</v>
+        <v>53</v>
       </c>
       <c r="C4" t="s">
-        <v>87</v>
+        <v>54</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>88</v>
+        <v>55</v>
       </c>
       <c r="E4">
         <v>4.9000000000000004</v>
@@ -1285,27 +1015,27 @@
         <v>2175</v>
       </c>
       <c r="G4" t="s">
-        <v>89</v>
+        <v>56</v>
       </c>
       <c r="H4" t="s">
-        <v>90</v>
+        <v>57</v>
       </c>
       <c r="I4" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>106</v>
+        <v>63</v>
       </c>
       <c r="B5" t="s">
-        <v>107</v>
+        <v>64</v>
       </c>
       <c r="C5" t="s">
-        <v>108</v>
+        <v>65</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>109</v>
+        <v>66</v>
       </c>
       <c r="E5">
         <v>4.8</v>
@@ -1314,27 +1044,27 @@
         <v>3971</v>
       </c>
       <c r="G5" t="s">
-        <v>110</v>
+        <v>67</v>
       </c>
       <c r="H5" t="s">
-        <v>111</v>
+        <v>68</v>
       </c>
       <c r="I5" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>112</v>
+        <v>69</v>
       </c>
       <c r="B6" t="s">
-        <v>113</v>
+        <v>70</v>
       </c>
       <c r="C6" t="s">
-        <v>114</v>
+        <v>71</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>115</v>
+        <v>72</v>
       </c>
       <c r="E6">
         <v>4.9000000000000004</v>
@@ -1343,27 +1073,27 @@
         <v>2609</v>
       </c>
       <c r="G6" t="s">
-        <v>116</v>
+        <v>73</v>
       </c>
       <c r="H6" t="s">
-        <v>117</v>
+        <v>74</v>
       </c>
       <c r="I6" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>123</v>
+        <v>80</v>
       </c>
       <c r="B7" t="s">
-        <v>124</v>
+        <v>81</v>
       </c>
       <c r="C7" t="s">
-        <v>125</v>
+        <v>82</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>126</v>
+        <v>83</v>
       </c>
       <c r="E7">
         <v>4.9000000000000004</v>
@@ -1372,27 +1102,27 @@
         <v>18966</v>
       </c>
       <c r="G7" t="s">
-        <v>127</v>
+        <v>84</v>
       </c>
       <c r="H7" t="s">
-        <v>128</v>
+        <v>85</v>
       </c>
       <c r="I7" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>134</v>
+        <v>91</v>
       </c>
       <c r="B8" t="s">
-        <v>135</v>
+        <v>92</v>
       </c>
       <c r="C8" t="s">
-        <v>136</v>
+        <v>93</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>137</v>
+        <v>94</v>
       </c>
       <c r="E8">
         <v>4.2</v>
@@ -1401,27 +1131,27 @@
         <v>6847</v>
       </c>
       <c r="G8" t="s">
-        <v>138</v>
+        <v>95</v>
       </c>
       <c r="H8" t="s">
-        <v>139</v>
+        <v>96</v>
       </c>
       <c r="I8" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>140</v>
+        <v>97</v>
       </c>
       <c r="B9" t="s">
-        <v>141</v>
+        <v>98</v>
       </c>
       <c r="C9" t="s">
-        <v>142</v>
+        <v>99</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>143</v>
+        <v>100</v>
       </c>
       <c r="E9">
         <v>4.5</v>
@@ -1430,27 +1160,27 @@
         <v>1409</v>
       </c>
       <c r="G9" t="s">
-        <v>144</v>
+        <v>101</v>
       </c>
       <c r="H9" t="s">
-        <v>145</v>
+        <v>102</v>
       </c>
       <c r="I9" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>166</v>
+        <v>112</v>
       </c>
       <c r="B10" t="s">
-        <v>167</v>
+        <v>113</v>
       </c>
       <c r="C10" t="s">
-        <v>168</v>
+        <v>114</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>169</v>
+        <v>115</v>
       </c>
       <c r="E10">
         <v>4.9000000000000004</v>
@@ -1459,27 +1189,27 @@
         <v>1204</v>
       </c>
       <c r="G10" t="s">
-        <v>170</v>
+        <v>116</v>
       </c>
       <c r="H10" t="s">
-        <v>171</v>
+        <v>117</v>
       </c>
       <c r="I10" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>186</v>
+        <v>123</v>
       </c>
       <c r="B11" t="s">
-        <v>187</v>
+        <v>124</v>
       </c>
       <c r="C11" t="s">
-        <v>188</v>
+        <v>125</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>189</v>
+        <v>126</v>
       </c>
       <c r="E11">
         <v>4.2</v>
@@ -1488,27 +1218,27 @@
         <v>2525</v>
       </c>
       <c r="G11" t="s">
-        <v>190</v>
+        <v>127</v>
       </c>
       <c r="H11" t="s">
-        <v>191</v>
+        <v>128</v>
       </c>
       <c r="I11" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>206</v>
+        <v>129</v>
       </c>
       <c r="B12" t="s">
-        <v>207</v>
+        <v>130</v>
       </c>
       <c r="C12" t="s">
-        <v>208</v>
+        <v>131</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>209</v>
+        <v>132</v>
       </c>
       <c r="E12">
         <v>4.4000000000000004</v>
@@ -1517,27 +1247,27 @@
         <v>5499</v>
       </c>
       <c r="G12" t="s">
-        <v>210</v>
+        <v>133</v>
       </c>
       <c r="H12" t="s">
-        <v>211</v>
+        <v>134</v>
       </c>
       <c r="I12" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>246</v>
+        <v>149</v>
       </c>
       <c r="B13" t="s">
-        <v>247</v>
+        <v>150</v>
       </c>
       <c r="C13" t="s">
-        <v>248</v>
+        <v>151</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>249</v>
+        <v>152</v>
       </c>
       <c r="E13">
         <v>4.9000000000000004</v>
@@ -1546,939 +1276,449 @@
         <v>741</v>
       </c>
       <c r="G13" t="s">
-        <v>250</v>
+        <v>153</v>
       </c>
       <c r="H13" t="s">
-        <v>251</v>
+        <v>154</v>
       </c>
       <c r="I13" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" t="s">
+        <v>23</v>
+      </c>
+      <c r="C14" t="s">
+        <v>24</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E14">
+        <v>4.8</v>
+      </c>
+      <c r="F14">
+        <v>10231</v>
+      </c>
+      <c r="G14" t="s">
         <v>26</v>
+      </c>
+      <c r="H14" t="s">
+        <v>160</v>
+      </c>
+      <c r="I14" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>41</v>
+      </c>
+      <c r="B15" t="s">
+        <v>42</v>
+      </c>
+      <c r="C15" t="s">
+        <v>43</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E15">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="F15">
+        <v>1549</v>
+      </c>
+      <c r="G15" t="s">
+        <v>45</v>
+      </c>
+      <c r="H15" t="s">
+        <v>162</v>
+      </c>
+      <c r="I15" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>9</v>
+        <v>75</v>
       </c>
       <c r="B16" t="s">
-        <v>10</v>
+        <v>76</v>
       </c>
       <c r="C16" t="s">
-        <v>11</v>
-      </c>
-      <c r="D16" t="s">
-        <v>12</v>
+        <v>77</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>78</v>
       </c>
       <c r="E16">
-        <v>4.4000000000000004</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="F16">
-        <v>6610</v>
+        <v>11809</v>
       </c>
       <c r="G16" t="s">
-        <v>13</v>
+        <v>79</v>
+      </c>
+      <c r="H16" t="s">
+        <v>163</v>
       </c>
       <c r="I16" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>15</v>
+        <v>135</v>
       </c>
       <c r="B17" t="s">
-        <v>16</v>
-      </c>
-      <c r="C17" t="s">
-        <v>17</v>
-      </c>
-      <c r="D17" t="s">
-        <v>18</v>
+        <v>136</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>137</v>
       </c>
       <c r="E17">
-        <v>4.3</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="F17">
-        <v>1045</v>
+        <v>7</v>
       </c>
       <c r="G17" t="s">
-        <v>19</v>
+        <v>138</v>
+      </c>
+      <c r="H17" t="s">
+        <v>165</v>
       </c>
       <c r="I17" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>27</v>
+        <v>155</v>
       </c>
       <c r="B18" t="s">
-        <v>28</v>
+        <v>156</v>
       </c>
       <c r="C18" t="s">
-        <v>29</v>
-      </c>
-      <c r="D18" t="s">
-        <v>30</v>
+        <v>157</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>158</v>
       </c>
       <c r="E18">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="F18">
-        <v>10231</v>
+        <v>934</v>
       </c>
       <c r="G18" t="s">
-        <v>31</v>
+        <v>159</v>
+      </c>
+      <c r="H18" t="s">
+        <v>166</v>
       </c>
       <c r="I18" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>32</v>
-      </c>
-      <c r="B19" t="s">
-        <v>33</v>
-      </c>
-      <c r="C19" t="s">
-        <v>34</v>
-      </c>
-      <c r="D19" t="s">
-        <v>35</v>
-      </c>
-      <c r="E19">
-        <v>4.9000000000000004</v>
-      </c>
-      <c r="F19">
-        <v>606</v>
-      </c>
-      <c r="G19" t="s">
-        <v>36</v>
-      </c>
-      <c r="I19" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>37</v>
-      </c>
-      <c r="B20" t="s">
-        <v>38</v>
-      </c>
-      <c r="C20" t="s">
-        <v>39</v>
-      </c>
-      <c r="E20">
-        <v>4.8</v>
-      </c>
-      <c r="F20">
-        <v>12047</v>
-      </c>
-      <c r="G20" t="s">
-        <v>40</v>
-      </c>
-      <c r="I20" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="B21" t="s">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="C21" t="s">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="D21" t="s">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="E21">
-        <v>4.7</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="F21">
-        <v>17321</v>
+        <v>6610</v>
       </c>
       <c r="G21" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="I21" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="B22" t="s">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="C22" t="s">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="D22" t="s">
-        <v>49</v>
+        <v>161</v>
       </c>
       <c r="E22">
-        <v>4.8</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="F22">
-        <v>3544</v>
+        <v>606</v>
       </c>
       <c r="G22" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="I22" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="B23" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="C23" t="s">
-        <v>53</v>
+        <v>33</v>
+      </c>
+      <c r="D23" t="s">
+        <v>34</v>
       </c>
       <c r="E23">
         <v>4.8</v>
       </c>
       <c r="F23">
-        <v>1036</v>
+        <v>11336</v>
       </c>
       <c r="G23" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="I23" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="B24" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="C24" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="D24" t="s">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="E24">
-        <v>4.8</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="F24">
-        <v>11336</v>
+        <v>597</v>
       </c>
       <c r="G24" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="I24" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
+        <v>58</v>
+      </c>
+      <c r="B25" t="s">
+        <v>59</v>
+      </c>
+      <c r="C25" t="s">
         <v>60</v>
       </c>
-      <c r="B25" t="s">
+      <c r="D25" t="s">
         <v>61</v>
       </c>
-      <c r="C25" t="s">
+      <c r="E25">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="F25">
+        <v>2668</v>
+      </c>
+      <c r="G25" t="s">
         <v>62</v>
-      </c>
-      <c r="D25" t="s">
-        <v>63</v>
-      </c>
-      <c r="E25">
-        <v>4.9000000000000004</v>
-      </c>
-      <c r="F25">
-        <v>597</v>
-      </c>
-      <c r="G25" t="s">
-        <v>64</v>
       </c>
       <c r="I25" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>65</v>
+        <v>86</v>
       </c>
       <c r="B26" t="s">
-        <v>66</v>
+        <v>87</v>
       </c>
       <c r="C26" t="s">
-        <v>67</v>
+        <v>88</v>
       </c>
       <c r="D26" t="s">
-        <v>68</v>
+        <v>89</v>
       </c>
       <c r="E26">
-        <v>4.9000000000000004</v>
+        <v>4.8</v>
       </c>
       <c r="F26">
-        <v>2117</v>
+        <v>1063</v>
       </c>
       <c r="G26" t="s">
-        <v>69</v>
+        <v>90</v>
       </c>
       <c r="I26" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>70</v>
+        <v>103</v>
       </c>
       <c r="B27" t="s">
-        <v>71</v>
+        <v>104</v>
       </c>
       <c r="C27" t="s">
-        <v>72</v>
+        <v>105</v>
+      </c>
+      <c r="D27" t="s">
+        <v>106</v>
       </c>
       <c r="E27">
-        <v>4.5</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="F27">
-        <v>7223</v>
+        <v>672</v>
       </c>
       <c r="G27" t="s">
-        <v>73</v>
+        <v>107</v>
       </c>
       <c r="I27" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>74</v>
+        <v>108</v>
       </c>
       <c r="B28" t="s">
-        <v>75</v>
+        <v>109</v>
       </c>
       <c r="C28" t="s">
-        <v>76</v>
+        <v>110</v>
       </c>
       <c r="D28" t="s">
-        <v>77</v>
+        <v>164</v>
       </c>
       <c r="E28">
-        <v>4.9000000000000004</v>
+        <v>4.7</v>
       </c>
       <c r="F28">
-        <v>1549</v>
+        <v>8648</v>
       </c>
       <c r="G28" t="s">
-        <v>78</v>
+        <v>111</v>
       </c>
       <c r="I28" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>91</v>
+        <v>118</v>
       </c>
       <c r="B29" t="s">
-        <v>92</v>
+        <v>119</v>
       </c>
       <c r="C29" t="s">
-        <v>93</v>
+        <v>120</v>
       </c>
       <c r="D29" t="s">
-        <v>94</v>
+        <v>121</v>
       </c>
       <c r="E29">
-        <v>4.4000000000000004</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="F29">
-        <v>2668</v>
+        <v>5648</v>
       </c>
       <c r="G29" t="s">
-        <v>95</v>
+        <v>122</v>
       </c>
       <c r="I29" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>96</v>
+        <v>139</v>
       </c>
       <c r="B30" t="s">
-        <v>97</v>
+        <v>140</v>
       </c>
       <c r="C30" t="s">
-        <v>98</v>
+        <v>141</v>
       </c>
       <c r="D30" t="s">
-        <v>99</v>
+        <v>142</v>
       </c>
       <c r="E30">
-        <v>4.4000000000000004</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="F30">
-        <v>3125</v>
+        <v>1603</v>
       </c>
       <c r="G30" t="s">
-        <v>100</v>
+        <v>143</v>
       </c>
       <c r="I30" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>101</v>
+        <v>144</v>
       </c>
       <c r="B31" t="s">
-        <v>102</v>
+        <v>145</v>
       </c>
       <c r="C31" t="s">
-        <v>103</v>
+        <v>146</v>
       </c>
       <c r="D31" t="s">
-        <v>104</v>
+        <v>147</v>
       </c>
       <c r="E31">
-        <v>4.9000000000000004</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="F31">
-        <v>741</v>
+        <v>1591</v>
       </c>
       <c r="G31" t="s">
-        <v>105</v>
+        <v>148</v>
       </c>
       <c r="I31" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
-        <v>118</v>
-      </c>
-      <c r="B32" t="s">
-        <v>119</v>
-      </c>
-      <c r="C32" t="s">
-        <v>120</v>
-      </c>
-      <c r="D32" t="s">
-        <v>121</v>
-      </c>
-      <c r="E32">
-        <v>4.9000000000000004</v>
-      </c>
-      <c r="F32">
-        <v>11809</v>
-      </c>
-      <c r="G32" t="s">
-        <v>122</v>
-      </c>
-      <c r="I32" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
-        <v>129</v>
-      </c>
-      <c r="B33" t="s">
-        <v>130</v>
-      </c>
-      <c r="C33" t="s">
-        <v>131</v>
-      </c>
-      <c r="D33" t="s">
-        <v>132</v>
-      </c>
-      <c r="E33">
-        <v>4.8</v>
-      </c>
-      <c r="F33">
-        <v>1063</v>
-      </c>
-      <c r="G33" t="s">
-        <v>133</v>
-      </c>
-      <c r="I33" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
-        <v>146</v>
-      </c>
-      <c r="B34" t="s">
-        <v>147</v>
-      </c>
-      <c r="C34" t="s">
-        <v>148</v>
-      </c>
-      <c r="D34" t="s">
-        <v>149</v>
-      </c>
-      <c r="E34">
-        <v>4.9000000000000004</v>
-      </c>
-      <c r="F34">
-        <v>672</v>
-      </c>
-      <c r="G34" t="s">
-        <v>150</v>
-      </c>
-      <c r="I34" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
-        <v>151</v>
-      </c>
-      <c r="B35" t="s">
-        <v>152</v>
-      </c>
-      <c r="C35" t="s">
-        <v>153</v>
-      </c>
-      <c r="D35" t="s">
-        <v>154</v>
-      </c>
-      <c r="E35">
-        <v>4.7</v>
-      </c>
-      <c r="F35">
-        <v>3194</v>
-      </c>
-      <c r="G35" t="s">
-        <v>155</v>
-      </c>
-      <c r="I35" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
-        <v>156</v>
-      </c>
-      <c r="B36" t="s">
-        <v>157</v>
-      </c>
-      <c r="C36" t="s">
-        <v>158</v>
-      </c>
-      <c r="D36" t="s">
-        <v>159</v>
-      </c>
-      <c r="E36">
-        <v>4.7</v>
-      </c>
-      <c r="F36">
-        <v>8648</v>
-      </c>
-      <c r="G36" t="s">
-        <v>160</v>
-      </c>
-      <c r="I36" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
-        <v>161</v>
-      </c>
-      <c r="B37" t="s">
-        <v>162</v>
-      </c>
-      <c r="C37" t="s">
-        <v>163</v>
-      </c>
-      <c r="D37" t="s">
-        <v>164</v>
-      </c>
-      <c r="E37">
-        <v>4.3</v>
-      </c>
-      <c r="F37">
-        <v>4734</v>
-      </c>
-      <c r="G37" t="s">
-        <v>165</v>
-      </c>
-      <c r="I37" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
-        <v>172</v>
-      </c>
-      <c r="B38" t="s">
-        <v>173</v>
-      </c>
-      <c r="C38" t="s">
-        <v>174</v>
-      </c>
-      <c r="E38">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="F38">
-        <v>5188</v>
-      </c>
-      <c r="G38" t="s">
-        <v>175</v>
-      </c>
-      <c r="I38" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
-        <v>176</v>
-      </c>
-      <c r="B39" t="s">
-        <v>177</v>
-      </c>
-      <c r="C39" t="s">
-        <v>178</v>
-      </c>
-      <c r="D39" t="s">
-        <v>179</v>
-      </c>
-      <c r="E39">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="F39">
-        <v>5648</v>
-      </c>
-      <c r="G39" t="s">
-        <v>180</v>
-      </c>
-      <c r="I39" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
-        <v>181</v>
-      </c>
-      <c r="B40" t="s">
-        <v>182</v>
-      </c>
-      <c r="C40" t="s">
-        <v>183</v>
-      </c>
-      <c r="D40" t="s">
-        <v>184</v>
-      </c>
-      <c r="E40">
-        <v>4.9000000000000004</v>
-      </c>
-      <c r="F40">
-        <v>13009</v>
-      </c>
-      <c r="G40" t="s">
-        <v>185</v>
-      </c>
-      <c r="I40" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
-        <v>192</v>
-      </c>
-      <c r="B41" t="s">
-        <v>193</v>
-      </c>
-      <c r="C41" t="s">
-        <v>194</v>
-      </c>
-      <c r="D41" t="s">
-        <v>195</v>
-      </c>
-      <c r="E41">
-        <v>4.7</v>
-      </c>
-      <c r="F41">
-        <v>4733</v>
-      </c>
-      <c r="G41" t="s">
-        <v>196</v>
-      </c>
-      <c r="I41" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
-        <v>197</v>
-      </c>
-      <c r="B42" t="s">
-        <v>198</v>
-      </c>
-      <c r="C42" t="s">
-        <v>199</v>
-      </c>
-      <c r="D42" t="s">
-        <v>200</v>
-      </c>
-      <c r="E42">
-        <v>4.2</v>
-      </c>
-      <c r="F42">
-        <v>5465</v>
-      </c>
-      <c r="G42" t="s">
-        <v>201</v>
-      </c>
-      <c r="I42" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
-        <v>202</v>
-      </c>
-      <c r="B43" t="s">
-        <v>203</v>
-      </c>
-      <c r="C43" t="s">
-        <v>204</v>
-      </c>
-      <c r="D43" t="s">
-        <v>200</v>
-      </c>
-      <c r="E43">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="F43">
-        <v>7031</v>
-      </c>
-      <c r="G43" t="s">
-        <v>205</v>
-      </c>
-      <c r="I43" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
-        <v>212</v>
-      </c>
-      <c r="B44" t="s">
-        <v>213</v>
-      </c>
-      <c r="C44" t="s">
-        <v>214</v>
-      </c>
-      <c r="D44" t="s">
-        <v>215</v>
-      </c>
-      <c r="E44">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="F44">
-        <v>11827</v>
-      </c>
-      <c r="G44" t="s">
-        <v>216</v>
-      </c>
-      <c r="I44" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
-        <v>217</v>
-      </c>
-      <c r="B45" t="s">
-        <v>218</v>
-      </c>
-      <c r="D45" t="s">
-        <v>219</v>
-      </c>
-      <c r="E45">
-        <v>4.9000000000000004</v>
-      </c>
-      <c r="F45">
-        <v>7</v>
-      </c>
-      <c r="G45" t="s">
-        <v>220</v>
-      </c>
-      <c r="I45" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
-        <v>221</v>
-      </c>
-      <c r="B46" t="s">
-        <v>222</v>
-      </c>
-      <c r="C46" t="s">
-        <v>223</v>
-      </c>
-      <c r="D46" t="s">
-        <v>224</v>
-      </c>
-      <c r="E46">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="F46">
-        <v>1603</v>
-      </c>
-      <c r="G46" t="s">
-        <v>225</v>
-      </c>
-      <c r="I46" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
-        <v>226</v>
-      </c>
-      <c r="B47" t="s">
-        <v>227</v>
-      </c>
-      <c r="C47" t="s">
-        <v>228</v>
-      </c>
-      <c r="D47" t="s">
-        <v>229</v>
-      </c>
-      <c r="E47">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="F47">
-        <v>1591</v>
-      </c>
-      <c r="G47" t="s">
-        <v>230</v>
-      </c>
-      <c r="I47" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
-        <v>231</v>
-      </c>
-      <c r="B48" t="s">
-        <v>232</v>
-      </c>
-      <c r="C48" t="s">
-        <v>233</v>
-      </c>
-      <c r="D48" t="s">
-        <v>234</v>
-      </c>
-      <c r="E48">
-        <v>4.9000000000000004</v>
-      </c>
-      <c r="F48">
-        <v>2456</v>
-      </c>
-      <c r="G48" t="s">
-        <v>235</v>
-      </c>
-      <c r="I48" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
-        <v>236</v>
-      </c>
-      <c r="B49" t="s">
-        <v>237</v>
-      </c>
-      <c r="C49" t="s">
-        <v>238</v>
-      </c>
-      <c r="D49" t="s">
-        <v>239</v>
-      </c>
-      <c r="E49">
-        <v>4.9000000000000004</v>
-      </c>
-      <c r="F49">
-        <v>2875</v>
-      </c>
-      <c r="G49" t="s">
-        <v>240</v>
-      </c>
-      <c r="I49" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
-        <v>241</v>
-      </c>
-      <c r="B50" t="s">
-        <v>242</v>
-      </c>
-      <c r="C50" t="s">
-        <v>243</v>
-      </c>
-      <c r="D50" t="s">
-        <v>244</v>
-      </c>
-      <c r="E50">
-        <v>4.7</v>
-      </c>
-      <c r="F50">
-        <v>5253</v>
-      </c>
-      <c r="G50" t="s">
-        <v>245</v>
-      </c>
-      <c r="I50" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
-        <v>252</v>
-      </c>
-      <c r="B51" t="s">
-        <v>253</v>
-      </c>
-      <c r="C51" t="s">
-        <v>254</v>
-      </c>
-      <c r="D51" t="s">
-        <v>255</v>
-      </c>
-      <c r="E51">
-        <v>4.3</v>
-      </c>
-      <c r="F51">
-        <v>934</v>
-      </c>
-      <c r="G51" t="s">
-        <v>256</v>
-      </c>
-      <c r="I51" t="s">
-        <v>14</v>
+      <c r="K31">
+        <v>500</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I51">
-    <sortCondition ref="I2:I51"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I32">
+    <sortCondition ref="I2:I32"/>
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/restaurant_crawler/restaurant_data_台北_麻辣鍋_20250910_135238_with_emails.xlsx
+++ b/restaurant_crawler/restaurant_data_台北_麻辣鍋_20250910_135238_with_emails.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\slow3\OneDrive\桌面\GitHubProjects\BYOB\restaurant_crawler\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B631ABB9-CA75-48CD-944C-0E9BDD21FA71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C213D6A0-BA5F-49CC-B734-E6ADB2ACB791}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="161">
   <si>
     <t>name</t>
   </si>
@@ -467,24 +467,6 @@
   </si>
   <si>
     <t>ChIJj1sXfN6rQjQRQQzAZzfGjN8</t>
-  </si>
-  <si>
-    <t>三分半海鮮鍋物</t>
-  </si>
-  <si>
-    <t>110台灣台北市信義區基隆路一段147巷5弄9號</t>
-  </si>
-  <si>
-    <t>02 2768 5553</t>
-  </si>
-  <si>
-    <t>https://www.facebook.com/3.5seafoodpot</t>
-  </si>
-  <si>
-    <t>ChIJQfEpbRCrQjQRlmtmfIQ9kIk</t>
-  </si>
-  <si>
-    <t>3.5minhotpot@gmail.com</t>
   </si>
   <si>
     <t>鼎王麻辣鍋(台北忠孝店)</t>
@@ -899,7 +881,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K31"/>
+  <dimension ref="A1:K30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -1258,57 +1240,57 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>149</v>
+        <v>22</v>
       </c>
       <c r="B13" t="s">
-        <v>150</v>
+        <v>23</v>
       </c>
       <c r="C13" t="s">
-        <v>151</v>
+        <v>24</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>152</v>
+        <v>25</v>
       </c>
       <c r="E13">
-        <v>4.9000000000000004</v>
+        <v>4.8</v>
       </c>
       <c r="F13">
-        <v>741</v>
+        <v>10231</v>
       </c>
       <c r="G13" t="s">
-        <v>153</v>
+        <v>26</v>
       </c>
       <c r="H13" t="s">
         <v>154</v>
       </c>
       <c r="I13" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="B14" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="C14" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="E14">
-        <v>4.8</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="F14">
-        <v>10231</v>
+        <v>1549</v>
       </c>
       <c r="G14" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="H14" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="I14" t="s">
         <v>14</v>
@@ -1316,28 +1298,28 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>41</v>
+        <v>75</v>
       </c>
       <c r="B15" t="s">
-        <v>42</v>
+        <v>76</v>
       </c>
       <c r="C15" t="s">
-        <v>43</v>
+        <v>77</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>44</v>
+        <v>78</v>
       </c>
       <c r="E15">
         <v>4.9000000000000004</v>
       </c>
       <c r="F15">
-        <v>1549</v>
+        <v>11809</v>
       </c>
       <c r="G15" t="s">
-        <v>45</v>
+        <v>79</v>
       </c>
       <c r="H15" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="I15" t="s">
         <v>14</v>
@@ -1345,28 +1327,25 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>75</v>
+        <v>135</v>
       </c>
       <c r="B16" t="s">
-        <v>76</v>
-      </c>
-      <c r="C16" t="s">
-        <v>77</v>
+        <v>136</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>78</v>
+        <v>137</v>
       </c>
       <c r="E16">
         <v>4.9000000000000004</v>
       </c>
       <c r="F16">
-        <v>11809</v>
+        <v>7</v>
       </c>
       <c r="G16" t="s">
-        <v>79</v>
+        <v>138</v>
       </c>
       <c r="H16" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="I16" t="s">
         <v>14</v>
@@ -1374,80 +1353,80 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="B17" t="s">
-        <v>136</v>
+        <v>150</v>
+      </c>
+      <c r="C17" t="s">
+        <v>151</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>137</v>
+        <v>152</v>
       </c>
       <c r="E17">
-        <v>4.9000000000000004</v>
+        <v>4.3</v>
       </c>
       <c r="F17">
-        <v>7</v>
+        <v>934</v>
       </c>
       <c r="G17" t="s">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="H17" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="I17" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>155</v>
-      </c>
-      <c r="B18" t="s">
-        <v>156</v>
-      </c>
-      <c r="C18" t="s">
-        <v>157</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="E18">
-        <v>4.3</v>
-      </c>
-      <c r="F18">
-        <v>934</v>
-      </c>
-      <c r="G18" t="s">
-        <v>159</v>
-      </c>
-      <c r="H18" t="s">
-        <v>166</v>
-      </c>
-      <c r="I18" t="s">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" t="s">
+        <v>10</v>
+      </c>
+      <c r="C20" t="s">
+        <v>11</v>
+      </c>
+      <c r="D20" t="s">
+        <v>12</v>
+      </c>
+      <c r="E20">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="F20">
+        <v>6610</v>
+      </c>
+      <c r="G20" t="s">
+        <v>13</v>
+      </c>
+      <c r="I20" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="B21" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="C21" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="D21" t="s">
-        <v>12</v>
+        <v>155</v>
       </c>
       <c r="E21">
-        <v>4.4000000000000004</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="F21">
-        <v>6610</v>
+        <v>606</v>
       </c>
       <c r="G21" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="I21" t="s">
         <v>14</v>
@@ -1455,25 +1434,25 @@
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B22" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C22" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D22" t="s">
-        <v>161</v>
+        <v>34</v>
       </c>
       <c r="E22">
-        <v>4.9000000000000004</v>
+        <v>4.8</v>
       </c>
       <c r="F22">
-        <v>606</v>
+        <v>11336</v>
       </c>
       <c r="G22" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I22" t="s">
         <v>14</v>
@@ -1481,25 +1460,25 @@
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="B23" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="C23" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D23" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E23">
-        <v>4.8</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="F23">
-        <v>11336</v>
+        <v>597</v>
       </c>
       <c r="G23" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="I23" t="s">
         <v>14</v>
@@ -1507,25 +1486,25 @@
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="B24" t="s">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="C24" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="D24" t="s">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="E24">
-        <v>4.9000000000000004</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="F24">
-        <v>597</v>
+        <v>2668</v>
       </c>
       <c r="G24" t="s">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="I24" t="s">
         <v>14</v>
@@ -1533,25 +1512,25 @@
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>58</v>
+        <v>86</v>
       </c>
       <c r="B25" t="s">
-        <v>59</v>
+        <v>87</v>
       </c>
       <c r="C25" t="s">
-        <v>60</v>
+        <v>88</v>
       </c>
       <c r="D25" t="s">
-        <v>61</v>
+        <v>89</v>
       </c>
       <c r="E25">
-        <v>4.4000000000000004</v>
+        <v>4.8</v>
       </c>
       <c r="F25">
-        <v>2668</v>
+        <v>1063</v>
       </c>
       <c r="G25" t="s">
-        <v>62</v>
+        <v>90</v>
       </c>
       <c r="I25" t="s">
         <v>14</v>
@@ -1559,25 +1538,25 @@
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="B26" t="s">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="C26" t="s">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="D26" t="s">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c r="E26">
-        <v>4.8</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="F26">
-        <v>1063</v>
+        <v>672</v>
       </c>
       <c r="G26" t="s">
-        <v>90</v>
+        <v>107</v>
       </c>
       <c r="I26" t="s">
         <v>14</v>
@@ -1585,25 +1564,25 @@
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="B27" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="C27" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="D27" t="s">
-        <v>106</v>
+        <v>158</v>
       </c>
       <c r="E27">
-        <v>4.9000000000000004</v>
+        <v>4.7</v>
       </c>
       <c r="F27">
-        <v>672</v>
+        <v>8648</v>
       </c>
       <c r="G27" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="I27" t="s">
         <v>14</v>
@@ -1611,25 +1590,25 @@
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="B28" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="C28" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="D28" t="s">
-        <v>164</v>
+        <v>121</v>
       </c>
       <c r="E28">
-        <v>4.7</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="F28">
-        <v>8648</v>
+        <v>5648</v>
       </c>
       <c r="G28" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="I28" t="s">
         <v>14</v>
@@ -1637,25 +1616,25 @@
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>118</v>
+        <v>139</v>
       </c>
       <c r="B29" t="s">
-        <v>119</v>
+        <v>140</v>
       </c>
       <c r="C29" t="s">
-        <v>120</v>
+        <v>141</v>
       </c>
       <c r="D29" t="s">
-        <v>121</v>
+        <v>142</v>
       </c>
       <c r="E29">
         <v>4.5999999999999996</v>
       </c>
       <c r="F29">
-        <v>5648</v>
+        <v>1603</v>
       </c>
       <c r="G29" t="s">
-        <v>122</v>
+        <v>143</v>
       </c>
       <c r="I29" t="s">
         <v>14</v>
@@ -1663,62 +1642,36 @@
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B30" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="C30" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="D30" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="E30">
         <v>4.5999999999999996</v>
       </c>
       <c r="F30">
-        <v>1603</v>
+        <v>1591</v>
       </c>
       <c r="G30" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="I30" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>144</v>
-      </c>
-      <c r="B31" t="s">
-        <v>145</v>
-      </c>
-      <c r="C31" t="s">
-        <v>146</v>
-      </c>
-      <c r="D31" t="s">
-        <v>147</v>
-      </c>
-      <c r="E31">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="F31">
-        <v>1591</v>
-      </c>
-      <c r="G31" t="s">
-        <v>148</v>
-      </c>
-      <c r="I31" t="s">
-        <v>14</v>
-      </c>
-      <c r="K31">
+      <c r="K30">
         <v>500</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I32">
-    <sortCondition ref="I2:I32"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I31">
+    <sortCondition ref="I2:I31"/>
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
